--- a/data/trans_orig/IP3101-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP3101-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2773</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10569</t>
+          <t>11253</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6711</t>
+          <t>6724</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17504</t>
+          <t>17585</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11089</t>
+          <t>11569</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24186</t>
+          <t>24605</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6420</t>
+          <t>6323</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16553</t>
+          <t>16592</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8700</t>
+          <t>9010</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>20308</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17194</t>
+          <t>17187</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32138</t>
+          <t>32442</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21190</t>
+          <t>21492</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38137</t>
+          <t>36700</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17061</t>
+          <t>17403</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31826</t>
+          <t>32359</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>42695</t>
+          <t>41804</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>62842</t>
+          <t>63079</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25064</t>
+          <t>25072</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41230</t>
+          <t>41467</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33011</t>
+          <t>33719</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50928</t>
+          <t>50924</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63549</t>
+          <t>62305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>87489</t>
+          <t>86025</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>31,86%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42418</t>
+          <t>43543</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>60324</t>
+          <t>61716</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>41465</t>
+          <t>41209</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59766</t>
+          <t>58921</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>88588</t>
+          <t>88995</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>113779</t>
+          <t>114808</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,52%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9013</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21025</t>
+          <t>20108</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8697</t>
+          <t>9142</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20638</t>
+          <t>20557</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20280</t>
+          <t>20853</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36491</t>
+          <t>37060</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10394</t>
+          <t>10351</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>22023</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15955</t>
+          <t>15845</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30447</t>
+          <t>30229</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29392</t>
+          <t>29900</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47522</t>
+          <t>48064</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24433</t>
+          <t>25194</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40240</t>
+          <t>41063</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34622</t>
+          <t>34104</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52630</t>
+          <t>53397</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>64354</t>
+          <t>62918</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>87869</t>
+          <t>87246</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31613</t>
+          <t>31369</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48910</t>
+          <t>48909</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>36664</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54110</t>
+          <t>54205</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70950</t>
+          <t>72308</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96729</t>
+          <t>98121</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,58%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70078</t>
+          <t>70327</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89997</t>
+          <t>91143</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>68061</t>
+          <t>67414</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>89258</t>
+          <t>89105</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>143086</t>
+          <t>143401</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>173056</t>
+          <t>174388</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,46%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3149</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11141</t>
+          <t>10830</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4998</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13899</t>
+          <t>14520</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>10324</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22296</t>
+          <t>23837</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5408</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14847</t>
+          <t>13896</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6785</t>
+          <t>6343</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16998</t>
+          <t>16587</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14134</t>
+          <t>14112</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27911</t>
+          <t>27127</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10781</t>
+          <t>11067</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22142</t>
+          <t>22536</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12169</t>
+          <t>12360</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24606</t>
+          <t>24990</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25788</t>
+          <t>25675</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>42538</t>
+          <t>42267</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18703</t>
+          <t>18414</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32997</t>
+          <t>32039</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17267</t>
+          <t>17087</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31289</t>
+          <t>31052</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>38914</t>
+          <t>39359</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>58531</t>
+          <t>58713</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,2%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61314</t>
+          <t>62405</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>78868</t>
+          <t>79552</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>68046</t>
+          <t>67230</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>85479</t>
+          <t>84347</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>134705</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>160619</t>
+          <t>160250</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>60,58%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8849</t>
+          <t>8402</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22077</t>
+          <t>21308</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>4542</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13792</t>
+          <t>14098</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15629</t>
+          <t>15750</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31606</t>
+          <t>30832</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9933</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22555</t>
+          <t>23151</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10986</t>
+          <t>10934</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24357</t>
+          <t>24262</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>24028</t>
+          <t>24475</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>42518</t>
+          <t>43127</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>33750</t>
+          <t>32903</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53813</t>
+          <t>51730</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>29160</t>
+          <t>28703</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>46223</t>
+          <t>46490</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>65633</t>
+          <t>68476</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>93251</t>
+          <t>93799</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22150</t>
+          <t>21733</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38847</t>
+          <t>38575</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30209</t>
+          <t>29778</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>47450</t>
+          <t>47910</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>55682</t>
+          <t>56431</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>81338</t>
+          <t>80538</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>84998</t>
+          <t>84460</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>108113</t>
+          <t>108289</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>82053</t>
+          <t>81790</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>103863</t>
+          <t>104259</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>174500</t>
+          <t>172720</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>208007</t>
+          <t>206888</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>52,68%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>31214</t>
+          <t>32150</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>51264</t>
+          <t>52636</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>33171</t>
+          <t>34202</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>53517</t>
+          <t>54354</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>70065</t>
+          <t>68388</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>98612</t>
+          <t>96368</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>39701</t>
+          <t>40964</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>62275</t>
+          <t>62382</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>53196</t>
+          <t>52640</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>77491</t>
+          <t>77637</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>98871</t>
+          <t>99196</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>130804</t>
+          <t>132716</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>104322</t>
+          <t>102864</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>136645</t>
+          <t>136221</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>107819</t>
+          <t>107080</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>138627</t>
+          <t>139084</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>219754</t>
+          <t>218005</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>263458</t>
+          <t>264686</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>111057</t>
+          <t>111690</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>143816</t>
+          <t>144523</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>128858</t>
+          <t>130302</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>164514</t>
+          <t>164122</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>250777</t>
+          <t>251542</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>298084</t>
+          <t>298049</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>279828</t>
+          <t>281288</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>320461</t>
+          <t>320540</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>278362</t>
+          <t>276220</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>319354</t>
+          <t>317766</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>571790</t>
+          <t>568474</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>631468</t>
+          <t>625617</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>47,73%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7530</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2491</t>
+          <t>2489</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11089</t>
+          <t>11490</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>4734</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15613</t>
+          <t>15799</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18280</t>
+          <t>19218</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7298</t>
+          <t>7543</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18686</t>
+          <t>19252</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16685</t>
+          <t>16958</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33179</t>
+          <t>32686</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>11717</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25773</t>
+          <t>24997</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15289</t>
+          <t>14547</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29525</t>
+          <t>28877</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>30077</t>
+          <t>29015</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>50543</t>
+          <t>48991</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14074</t>
+          <t>14884</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28538</t>
+          <t>28300</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17742</t>
+          <t>17699</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33088</t>
+          <t>33317</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35081</t>
+          <t>35649</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56452</t>
+          <t>56026</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68387</t>
+          <t>68548</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87495</t>
+          <t>87678</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>69017</t>
+          <t>68071</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>89028</t>
+          <t>87188</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>143433</t>
+          <t>142293</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>171395</t>
+          <t>171056</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>62,23%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14574</t>
+          <t>14098</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6591</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16408</t>
+          <t>16818</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13343</t>
+          <t>13277</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28271</t>
+          <t>26904</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7343</t>
+          <t>7257</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18127</t>
+          <t>17894</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14146</t>
+          <t>13607</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28190</t>
+          <t>28730</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24170</t>
+          <t>24256</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>41794</t>
+          <t>40901</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22469</t>
+          <t>22470</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39200</t>
+          <t>37472</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25639</t>
+          <t>26176</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>42952</t>
+          <t>43490</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>52137</t>
+          <t>52223</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>76140</t>
+          <t>75884</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19006</t>
+          <t>19052</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34215</t>
+          <t>34714</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18486</t>
+          <t>18469</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33694</t>
+          <t>33976</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41641</t>
+          <t>41376</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62952</t>
+          <t>64289</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>104574</t>
+          <t>104641</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>125936</t>
+          <t>125244</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>104485</t>
+          <t>103233</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>128099</t>
+          <t>128365</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>213306</t>
+          <t>216121</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>245518</t>
+          <t>247570</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>62,27%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>437</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4852</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7015</t>
+          <t>6977</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2298</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9057</t>
+          <t>9477</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14175</t>
+          <t>14481</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3827</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11633</t>
+          <t>11986</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11262</t>
+          <t>10652</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22576</t>
+          <t>23412</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15103</t>
+          <t>15662</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28835</t>
+          <t>29621</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18899</t>
+          <t>18767</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33980</t>
+          <t>34231</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>38532</t>
+          <t>37867</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>59480</t>
+          <t>59038</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14718</t>
+          <t>14671</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27653</t>
+          <t>27830</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25890</t>
+          <t>25385</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41894</t>
+          <t>41161</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43375</t>
+          <t>43664</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>64426</t>
+          <t>65061</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>79551</t>
+          <t>79957</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>98218</t>
+          <t>97589</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>70427</t>
+          <t>71197</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>89924</t>
+          <t>89937</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>154870</t>
+          <t>156061</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>183393</t>
+          <t>182807</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,62%</t>
         </is>
       </c>
     </row>
@@ -6425,7 +6425,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5786</t>
+          <t>5982</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2838</t>
+          <t>2773</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11585</t>
+          <t>10947</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3612</t>
+          <t>3564</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13715</t>
+          <t>13128</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7697</t>
+          <t>7641</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19548</t>
+          <t>19351</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17326</t>
+          <t>16007</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>15809</t>
+          <t>15994</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>31183</t>
+          <t>32238</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>26785</t>
+          <t>26553</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>45283</t>
+          <t>45241</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25764</t>
+          <t>25061</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>43245</t>
+          <t>43221</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>56291</t>
+          <t>57009</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>82002</t>
+          <t>81888</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,44%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29163</t>
+          <t>29355</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>48895</t>
+          <t>48766</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21939</t>
+          <t>21150</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38113</t>
+          <t>37473</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>55630</t>
+          <t>55141</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>79700</t>
+          <t>80484</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>90569</t>
+          <t>91218</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>114567</t>
+          <t>114359</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>99700</t>
+          <t>102351</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>123531</t>
+          <t>124825</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>199631</t>
+          <t>200178</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>231453</t>
+          <t>233590</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>61,16%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10505</t>
+          <t>10349</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>23396</t>
+          <t>23061</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18300</t>
+          <t>17378</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>34228</t>
+          <t>34647</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>31751</t>
+          <t>31252</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>51810</t>
+          <t>52981</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>34426</t>
+          <t>35886</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>56918</t>
+          <t>56635</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>40200</t>
+          <t>39880</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>62764</t>
+          <t>61760</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>81460</t>
+          <t>80508</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>111356</t>
+          <t>111312</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>89343</t>
+          <t>90944</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>120184</t>
+          <t>121122</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>99467</t>
+          <t>97450</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>132636</t>
+          <t>132219</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>197765</t>
+          <t>197069</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>242996</t>
+          <t>239843</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>91921</t>
+          <t>91566</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>121819</t>
+          <t>124240</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>97089</t>
+          <t>96117</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>129410</t>
+          <t>130488</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>197594</t>
+          <t>193966</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>242001</t>
+          <t>242135</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>361613</t>
+          <t>361213</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>404971</t>
+          <t>404376</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>366242</t>
+          <t>367532</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>408740</t>
+          <t>409263</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>740109</t>
+          <t>742663</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>801221</t>
+          <t>805533</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,83%</t>
         </is>
       </c>
     </row>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>664</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6706</t>
+          <t>6244</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3151</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11583</t>
+          <t>11945</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>5069</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14409</t>
+          <t>15506</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5018</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14644</t>
+          <t>14619</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12382</t>
+          <t>12328</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9577</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23481</t>
+          <t>23017</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14927</t>
+          <t>15180</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29629</t>
+          <t>29753</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13781</t>
+          <t>13309</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28103</t>
+          <t>27867</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32562</t>
+          <t>32451</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53258</t>
+          <t>52406</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23346</t>
+          <t>23047</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39307</t>
+          <t>39915</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22514</t>
+          <t>22648</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38946</t>
+          <t>38928</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50310</t>
+          <t>50388</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73677</t>
+          <t>74699</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,44%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>50573</t>
+          <t>50833</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69071</t>
+          <t>70016</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64611</t>
+          <t>64520</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>84444</t>
+          <t>84188</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>121522</t>
+          <t>121771</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>149370</t>
+          <t>148024</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>56,36%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7813</t>
+          <t>7810</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4308</t>
+          <t>4080</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13576</t>
+          <t>13282</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6850</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18226</t>
+          <t>18058</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5207</t>
+          <t>5144</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14448</t>
+          <t>14458</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8440</t>
+          <t>8647</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19817</t>
+          <t>20186</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16249</t>
+          <t>16604</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31242</t>
+          <t>31043</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24723</t>
+          <t>24841</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40877</t>
+          <t>41679</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23222</t>
+          <t>23261</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39332</t>
+          <t>39619</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>51062</t>
+          <t>51704</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>75093</t>
+          <t>74306</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37933</t>
+          <t>37030</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56249</t>
+          <t>55667</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28714</t>
+          <t>29229</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46521</t>
+          <t>47298</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70131</t>
+          <t>70722</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97418</t>
+          <t>95913</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>91407</t>
+          <t>90433</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>113770</t>
+          <t>111548</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>107737</t>
+          <t>108849</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>131449</t>
+          <t>132261</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>206132</t>
+          <t>207109</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>237648</t>
+          <t>237680</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,02%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>519</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4780</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10226</t>
+          <t>10114</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12738</t>
+          <t>13068</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>7992</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19034</t>
+          <t>18690</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>4058</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12141</t>
+          <t>12576</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14532</t>
+          <t>14268</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28163</t>
+          <t>28090</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21227</t>
+          <t>21343</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>36655</t>
+          <t>36055</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15870</t>
+          <t>16400</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30225</t>
+          <t>31037</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>41285</t>
+          <t>40964</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>62732</t>
+          <t>62867</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18663</t>
+          <t>19457</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32503</t>
+          <t>32813</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29388</t>
+          <t>29417</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46275</t>
+          <t>46538</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51687</t>
+          <t>52779</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>74397</t>
+          <t>76064</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>67645</t>
+          <t>68172</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>86435</t>
+          <t>87474</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>74998</t>
+          <t>74437</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>94893</t>
+          <t>95347</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>147967</t>
+          <t>149422</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>176381</t>
+          <t>177173</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>58,27%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>8326</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10516</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5217</t>
+          <t>5057</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15718</t>
+          <t>16135</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>3278</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12575</t>
+          <t>12961</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10077</t>
+          <t>10749</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22602</t>
+          <t>23201</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>16058</t>
+          <t>15327</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>31332</t>
+          <t>30670</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13999</t>
+          <t>14243</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28596</t>
+          <t>30156</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>18788</t>
+          <t>18999</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>35395</t>
+          <t>34191</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>36321</t>
+          <t>38160</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>58843</t>
+          <t>59513</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,62%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>35624</t>
+          <t>35350</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55785</t>
+          <t>55129</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37088</t>
+          <t>36741</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>56356</t>
+          <t>56693</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>77790</t>
+          <t>77314</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>106103</t>
+          <t>105936</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,8%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>103728</t>
+          <t>102357</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>126276</t>
+          <t>126086</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>84654</t>
+          <t>84659</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>107247</t>
+          <t>106444</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>194523</t>
+          <t>195524</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>227514</t>
+          <t>227829</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,79%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7185</t>
+          <t>7143</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18304</t>
+          <t>18269</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17818</t>
+          <t>18099</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>35293</t>
+          <t>34696</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>27705</t>
+          <t>28435</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>47798</t>
+          <t>47792</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29067</t>
+          <t>29039</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>49439</t>
+          <t>47999</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>33056</t>
+          <t>33591</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>53558</t>
+          <t>54521</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>67442</t>
+          <t>67899</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>94802</t>
+          <t>95817</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>87713</t>
+          <t>89453</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>118517</t>
+          <t>119488</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>84801</t>
+          <t>84749</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>116741</t>
+          <t>115536</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>182903</t>
+          <t>182671</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>228309</t>
+          <t>225981</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>131878</t>
+          <t>130459</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>165613</t>
+          <t>165816</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>134215</t>
+          <t>136184</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>169797</t>
+          <t>173362</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>273208</t>
+          <t>277444</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>324835</t>
+          <t>323854</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -11196,47 +11196,47 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>332376</t>
+          <t>333778</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
+          <t>374509</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>54,1%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>50,97%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>57,19%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
           <t>375301</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>54,1%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>50,76%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>57,31%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>541</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>375301</t>
-        </is>
-      </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>353823</t>
+          <t>353209</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>398210</t>
+          <t>396658</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>698054</t>
+          <t>697862</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>760756</t>
+          <t>761185</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,36%</t>
         </is>
       </c>
     </row>
